--- a/data/demo/Megaluz-Traffic-2026-07-28~2026-07-28.xlsx
+++ b/data/demo/Megaluz-Traffic-2026-07-28~2026-07-28.xlsx
@@ -569,7 +569,7 @@
     <t>603059761601319</t>
   </si>
   <si>
-    <t>Altavoz Inalámbrico Portátil con Diseño Retro, Bajos Optimizados y Sonido 3D Envolvente,Compatible con TF/FM/AUX, Conexión BT TWS. Ideal para Home Theater, Fiestas y Regalos​</t>
+    <t>Altavoz Inalámbrico Portátil con Diseño Retro, Subwoofer Integrado y Sonido 3D Envolvente Compatible con TF/FM/AUX, Conexión BT TWS, Graves Potentes, Entrada de Energía Tipo C. Ideal para Cine en Casa, Fiestas, Regalos y Sistemas de Audio al Aire Libre</t>
   </si>
   <si>
     <t>1118</t>
